--- a/uploads/forest_land_excels/forest_land.xlsx
+++ b/uploads/forest_land_excels/forest_land.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maasuser\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD307539-E702-4B31-86FC-7363F69959F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BF46104-16DA-486E-B805-5D8F03807A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="42">
   <si>
     <t>District</t>
   </si>
@@ -545,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7369F36-A5A2-42C2-8596-EBE582C22F5C}">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="15.85546875" customWidth="1"/>
@@ -599,141 +599,102 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4" t="s">
+    <row r="2" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="1">
+        <v>65</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="1">
+        <v>16</v>
+      </c>
+      <c r="L2" s="1">
+        <v>12.2</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="1">
-        <v>65</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="1" t="s">
+      <c r="F3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="3">
+        <v>72</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" s="1">
-        <v>16</v>
-      </c>
-      <c r="L3" s="1">
-        <v>12.2</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="3">
-        <v>72</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K3" s="3">
         <v>12.5</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L3" s="3">
         <v>10.75</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
+    <row r="4" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
